--- a/DQ_ENGINE/config/DQ_RDS_config.xlsx
+++ b/DQ_ENGINE/config/DQ_RDS_config.xlsx
@@ -142,12 +142,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D590"/>
+  <dimension ref="A1:C590"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -166,11 +165,6 @@
           <t>ACTIVE_IND</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t>NUMERIC_BASIC_IND</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -188,11 +182,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -210,11 +199,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -232,11 +216,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -254,11 +233,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -276,11 +250,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -298,11 +267,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -320,11 +284,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -342,11 +301,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -364,11 +318,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -386,11 +335,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -408,11 +352,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -430,11 +369,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -452,11 +386,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -474,11 +403,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -496,11 +420,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -518,11 +437,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -540,11 +454,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -562,11 +471,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -584,11 +488,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -606,11 +505,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -628,11 +522,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -650,11 +539,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -672,11 +556,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -694,11 +573,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -716,11 +590,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -738,11 +607,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -760,11 +624,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -782,11 +641,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -804,11 +658,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -826,11 +675,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -848,11 +692,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -870,11 +709,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -892,11 +726,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -914,11 +743,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -936,11 +760,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -958,11 +777,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -980,11 +794,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1002,11 +811,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1024,11 +828,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1046,11 +845,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1068,11 +862,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1090,11 +879,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1112,11 +896,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1134,11 +913,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1156,11 +930,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1178,11 +947,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1200,11 +964,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1222,11 +981,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1244,11 +998,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1266,11 +1015,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1288,11 +1032,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1310,11 +1049,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1332,11 +1066,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1354,11 +1083,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1376,11 +1100,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1398,11 +1117,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1420,11 +1134,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1442,11 +1151,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1464,11 +1168,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1486,11 +1185,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1508,11 +1202,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1530,11 +1219,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1552,11 +1236,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1574,11 +1253,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1596,11 +1270,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1618,11 +1287,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1640,11 +1304,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1662,11 +1321,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1684,11 +1338,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1706,11 +1355,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1728,11 +1372,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1750,11 +1389,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1772,11 +1406,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1794,11 +1423,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1816,11 +1440,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1838,11 +1457,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1860,11 +1474,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1882,11 +1491,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1904,11 +1508,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1926,11 +1525,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1948,11 +1542,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1970,11 +1559,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1992,11 +1576,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2014,11 +1593,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2036,11 +1610,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2058,11 +1627,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2080,11 +1644,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2102,11 +1661,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2124,11 +1678,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2146,11 +1695,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2168,11 +1712,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2190,11 +1729,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2212,11 +1746,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2234,11 +1763,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2256,11 +1780,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2278,11 +1797,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2300,11 +1814,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2322,11 +1831,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2344,11 +1848,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2366,11 +1865,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2388,11 +1882,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2410,11 +1899,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2432,11 +1916,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2454,11 +1933,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2476,11 +1950,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2498,11 +1967,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2520,11 +1984,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2542,11 +2001,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2564,11 +2018,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2586,11 +2035,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2608,11 +2052,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2630,11 +2069,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2652,11 +2086,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2674,11 +2103,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2696,11 +2120,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2718,11 +2137,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2740,11 +2154,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2762,11 +2171,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2784,11 +2188,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2806,11 +2205,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2828,11 +2222,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2850,11 +2239,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2872,11 +2256,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2894,11 +2273,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2916,11 +2290,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2938,11 +2307,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2960,11 +2324,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2982,11 +2341,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3004,11 +2358,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3026,11 +2375,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3048,11 +2392,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3070,11 +2409,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3092,11 +2426,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3114,11 +2443,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3136,11 +2460,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3158,11 +2477,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3180,11 +2494,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3202,11 +2511,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3224,11 +2528,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3246,11 +2545,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3268,11 +2562,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3290,11 +2579,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3312,11 +2596,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3334,11 +2613,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3356,11 +2630,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3378,11 +2647,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3400,11 +2664,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3422,11 +2681,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3444,11 +2698,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3466,11 +2715,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3488,11 +2732,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3510,11 +2749,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3532,11 +2766,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3554,11 +2783,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3576,11 +2800,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3598,11 +2817,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3620,11 +2834,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3642,11 +2851,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3664,11 +2868,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3686,11 +2885,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3708,11 +2902,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3730,11 +2919,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3752,11 +2936,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3774,11 +2953,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3796,11 +2970,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3818,11 +2987,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3840,11 +3004,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3862,11 +3021,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3884,11 +3038,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3906,11 +3055,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3928,11 +3072,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3950,11 +3089,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3972,11 +3106,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3994,11 +3123,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4016,11 +3140,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4038,11 +3157,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4060,11 +3174,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4082,11 +3191,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4104,11 +3208,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4126,11 +3225,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4148,11 +3242,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4170,11 +3259,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4192,11 +3276,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4214,11 +3293,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4236,11 +3310,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4258,11 +3327,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4280,11 +3344,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4302,11 +3361,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4324,11 +3378,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4346,11 +3395,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4368,11 +3412,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4390,11 +3429,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4412,11 +3446,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4434,11 +3463,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4456,11 +3480,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4478,11 +3497,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4500,11 +3514,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4522,11 +3531,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4544,11 +3548,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4566,11 +3565,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4588,11 +3582,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4610,11 +3599,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4632,11 +3616,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4654,11 +3633,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4676,11 +3650,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4698,11 +3667,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4720,11 +3684,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4742,11 +3701,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4764,11 +3718,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4786,11 +3735,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4808,11 +3752,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4830,11 +3769,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4852,11 +3786,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4874,11 +3803,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4896,11 +3820,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4918,11 +3837,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4940,11 +3854,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4962,11 +3871,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4984,11 +3888,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5006,11 +3905,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5028,11 +3922,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -5050,11 +3939,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5072,11 +3956,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5094,11 +3973,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5116,11 +3990,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5138,11 +4007,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5160,11 +4024,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5182,11 +4041,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -5204,11 +4058,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -5226,11 +4075,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5248,11 +4092,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -5270,11 +4109,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5292,11 +4126,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5314,11 +4143,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -5336,11 +4160,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5358,11 +4177,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5380,11 +4194,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5402,11 +4211,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -5424,11 +4228,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5446,11 +4245,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5468,11 +4262,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5490,11 +4279,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5512,11 +4296,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5534,11 +4313,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5556,11 +4330,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5578,11 +4347,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5600,11 +4364,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5622,11 +4381,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5644,11 +4398,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5666,11 +4415,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5688,11 +4432,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5710,11 +4449,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5732,11 +4466,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5754,11 +4483,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5776,11 +4500,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5798,11 +4517,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5820,11 +4534,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5842,11 +4551,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5864,11 +4568,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5886,11 +4585,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5908,11 +4602,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5930,11 +4619,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5952,11 +4636,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5974,11 +4653,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5996,11 +4670,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6018,11 +4687,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6040,11 +4704,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6062,11 +4721,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6084,11 +4738,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6106,11 +4755,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6128,11 +4772,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6150,11 +4789,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6172,11 +4806,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6194,11 +4823,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6216,11 +4840,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6238,11 +4857,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6260,11 +4874,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6282,11 +4891,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6304,11 +4908,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6326,11 +4925,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6348,11 +4942,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6370,11 +4959,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6392,11 +4976,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6414,11 +4993,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6436,11 +5010,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6458,11 +5027,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6480,11 +5044,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6502,11 +5061,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6524,11 +5078,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6546,11 +5095,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6568,11 +5112,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6590,11 +5129,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6612,11 +5146,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6634,11 +5163,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6656,11 +5180,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6678,11 +5197,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6700,11 +5214,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -6722,11 +5231,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -6744,11 +5248,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -6766,11 +5265,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -6788,11 +5282,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -6810,11 +5299,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6832,11 +5316,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6854,11 +5333,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6876,11 +5350,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6898,11 +5367,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6920,11 +5384,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6942,11 +5401,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6964,11 +5418,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6986,11 +5435,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7008,11 +5452,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7030,11 +5469,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7052,11 +5486,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7074,11 +5503,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7096,11 +5520,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7118,11 +5537,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7140,11 +5554,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7162,11 +5571,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7184,11 +5588,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7206,11 +5605,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7228,11 +5622,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7250,11 +5639,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7272,11 +5656,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7294,11 +5673,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7316,11 +5690,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7338,11 +5707,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7360,11 +5724,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7382,11 +5741,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7404,11 +5758,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7426,11 +5775,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7448,11 +5792,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7470,11 +5809,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7492,11 +5826,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7514,11 +5843,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -7536,11 +5860,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -7558,11 +5877,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -7580,11 +5894,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -7602,11 +5911,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -7624,11 +5928,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -7646,11 +5945,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -7668,11 +5962,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -7690,11 +5979,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -7712,11 +5996,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -7734,11 +6013,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -7756,11 +6030,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -7778,11 +6047,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -7800,11 +6064,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -7822,11 +6081,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -7844,11 +6098,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -7866,11 +6115,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -7888,11 +6132,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -7910,11 +6149,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -7932,11 +6166,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -7954,11 +6183,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -7976,11 +6200,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -7998,11 +6217,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -8020,11 +6234,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -8042,11 +6251,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -8064,11 +6268,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8086,11 +6285,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8108,11 +6302,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8130,11 +6319,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8152,11 +6336,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8174,11 +6353,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8196,11 +6370,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8218,11 +6387,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8240,11 +6404,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8262,11 +6421,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8284,11 +6438,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8306,11 +6455,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8328,11 +6472,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -8350,11 +6489,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -8372,11 +6506,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -8394,11 +6523,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -8416,11 +6540,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -8438,11 +6557,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -8460,11 +6574,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -8482,11 +6591,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8504,11 +6608,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8526,11 +6625,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -8548,11 +6642,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -8570,11 +6659,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -8592,11 +6676,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -8614,11 +6693,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -8636,11 +6710,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -8658,11 +6727,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -8680,11 +6744,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -8702,11 +6761,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -8724,11 +6778,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -8746,11 +6795,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -8768,11 +6812,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -8790,11 +6829,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -8812,11 +6846,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -8834,11 +6863,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -8856,11 +6880,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -8878,11 +6897,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -8900,11 +6914,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -8922,11 +6931,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -8944,11 +6948,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -8966,11 +6965,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -8988,11 +6982,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -9010,11 +6999,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -9032,11 +7016,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -9054,11 +7033,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -9076,11 +7050,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -9098,11 +7067,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -9120,11 +7084,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -9142,11 +7101,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -9164,11 +7118,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -9186,11 +7135,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -9208,11 +7152,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -9230,11 +7169,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -9252,11 +7186,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -9274,11 +7203,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -9296,11 +7220,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -9318,11 +7237,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -9340,11 +7254,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -9362,11 +7271,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -9384,11 +7288,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -9406,11 +7305,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -9428,11 +7322,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -9450,11 +7339,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -9472,11 +7356,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -9494,11 +7373,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -9516,11 +7390,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -9538,11 +7407,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -9560,11 +7424,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -9582,11 +7441,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -9604,11 +7458,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -9626,11 +7475,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -9648,11 +7492,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -9670,11 +7509,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -9692,11 +7526,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -9714,11 +7543,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -9736,11 +7560,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -9758,11 +7577,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -9780,11 +7594,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -9802,11 +7611,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -9824,11 +7628,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -9846,11 +7645,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -9868,11 +7662,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -9890,11 +7679,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -9912,11 +7696,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -9934,11 +7713,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -9956,11 +7730,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -9978,11 +7747,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -10000,11 +7764,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -10022,11 +7781,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -10044,11 +7798,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -10066,11 +7815,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -10088,11 +7832,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -10110,11 +7849,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -10132,11 +7866,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -10154,11 +7883,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -10176,11 +7900,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -10198,11 +7917,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -10220,11 +7934,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -10242,11 +7951,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -10264,11 +7968,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -10286,11 +7985,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -10308,11 +8002,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -10330,11 +8019,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -10352,11 +8036,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -10374,11 +8053,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -10396,11 +8070,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -10418,11 +8087,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -10440,11 +8104,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -10462,11 +8121,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -10484,11 +8138,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -10506,11 +8155,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -10528,11 +8172,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -10550,11 +8189,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -10572,11 +8206,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -10594,11 +8223,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -10616,11 +8240,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -10638,11 +8257,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -10660,11 +8274,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -10682,11 +8291,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -10704,11 +8308,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -10726,11 +8325,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -10748,11 +8342,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -10770,11 +8359,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -10792,11 +8376,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -10814,11 +8393,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -10836,11 +8410,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -10858,11 +8427,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -10880,11 +8444,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -10902,11 +8461,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -10924,11 +8478,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -10946,11 +8495,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -10968,11 +8512,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -10990,11 +8529,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -11012,11 +8546,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -11034,11 +8563,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -11056,11 +8580,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -11078,11 +8597,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -11100,11 +8614,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -11122,11 +8631,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -11144,11 +8648,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -11166,11 +8665,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -11188,11 +8682,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -11210,11 +8699,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -11232,11 +8716,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -11254,11 +8733,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -11276,11 +8750,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -11298,11 +8767,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -11320,11 +8784,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -11342,11 +8801,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -11364,11 +8818,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -11386,11 +8835,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -11408,11 +8852,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -11430,11 +8869,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -11452,11 +8886,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -11474,11 +8903,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -11496,11 +8920,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -11518,11 +8937,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -11540,11 +8954,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -11562,11 +8971,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -11584,11 +8988,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -11606,11 +9005,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -11628,11 +9022,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -11650,11 +9039,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -11672,11 +9056,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -11694,11 +9073,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -11716,11 +9090,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -11738,11 +9107,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -11760,11 +9124,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -11782,11 +9141,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -11804,11 +9158,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -11826,11 +9175,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -11848,11 +9192,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -11870,11 +9209,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -11892,11 +9226,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -11914,11 +9243,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -11936,11 +9260,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -11958,11 +9277,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -11980,11 +9294,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -12002,11 +9311,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -12024,11 +9328,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -12046,11 +9345,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -12068,11 +9362,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D542" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -12090,11 +9379,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -12112,11 +9396,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -12134,11 +9413,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -12156,11 +9430,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -12178,11 +9447,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -12200,11 +9464,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -12222,11 +9481,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -12244,11 +9498,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -12266,11 +9515,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -12288,11 +9532,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -12310,11 +9549,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -12332,11 +9566,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -12354,11 +9583,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -12376,11 +9600,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -12398,11 +9617,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -12420,11 +9634,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -12442,11 +9651,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -12464,11 +9668,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -12486,11 +9685,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -12508,11 +9702,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -12530,11 +9719,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -12552,11 +9736,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -12574,11 +9753,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -12596,11 +9770,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -12618,11 +9787,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D567" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -12640,11 +9804,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -12662,11 +9821,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -12684,11 +9838,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -12706,11 +9855,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -12728,11 +9872,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -12750,11 +9889,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D573" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -12772,11 +9906,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -12794,11 +9923,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -12816,11 +9940,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -12838,11 +9957,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -12860,11 +9974,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -12882,11 +9991,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -12904,11 +10008,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D580" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -12926,11 +10025,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -12948,11 +10042,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -12970,11 +10059,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -12992,11 +10076,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D584" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -13014,11 +10093,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D585" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -13036,11 +10110,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D586" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -13058,11 +10127,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -13080,11 +10144,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -13102,11 +10161,6 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -13124,22 +10178,14 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D590"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:C590"/>
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Choose a listed value" error="Use the dropdown values." sqref="B2:B10000">
       <formula1>"NUMERIC,CATEGORICAL,DATE,IDENTIFIER"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Choose a listed value" error="Use the dropdown values." sqref="C2:C10000">
-      <formula1>"Y,N"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Choose a listed value" error="Use the dropdown values." sqref="D2:D10000">
       <formula1>"Y,N"</formula1>
     </dataValidation>
   </dataValidations>

--- a/DQ_ENGINE/config/DQ_RDS_config.xlsx
+++ b/DQ_ENGINE/config/DQ_RDS_config.xlsx
@@ -5,6 +5,7 @@
     <sheet name="Project" sheetId="1" r:id="rId1"/>
     <sheet name="Fields" sheetId="2" r:id="rId2"/>
     <sheet name="Settings" sheetId="3" r:id="rId3"/>
+    <sheet name="SpecialValues" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -10241,4 +10242,579 @@
   </sheetData>
   <autoFilter ref="A1:D2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C33"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>FIELD_TYPE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>SPECIAL_VALUE</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ACTIVE_IND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-99999</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-999999</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-999998</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-99998</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>-99997</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-9999</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>-9998</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>-999997</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>-999993</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>-999</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>-999995</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>999999</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>999998</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>999990</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>99999</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>99998</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>999.99</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>999.88</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>9999</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NUMERIC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>9998</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>#N/A</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CATEGORICAL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C33"/>
+</worksheet>
 </file>
--- a/DQ_ENGINE/config/DQ_RDS_config.xlsx
+++ b/DQ_ENGINE/config/DQ_RDS_config.xlsx
@@ -10195,12 +10195,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:G2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10224,6 +10225,21 @@
           <t>OUTLIER_SD_MULTIPLIER</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>PROFILE_OVERALL</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>PROFILE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t>PROFILE_YEARLY</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -10238,9 +10254,29 @@
       <c r="D2">
         <v>3</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:G2"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Choose Y or N" error="Select Y or N." sqref="E2:G2">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+  </dataValidations>
 </worksheet>
 </file>
 
